--- a/2026/ANATOLE FRANCE/FEBRERO/ANATOLE-Febrero.xlsx
+++ b/2026/ANATOLE FRANCE/FEBRERO/ANATOLE-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\FEBRERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EC50D4-40C9-4101-B3CA-9E7246F3347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F123E-16CE-4313-B573-542879B0CE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="166">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -526,6 +521,9 @@
   </si>
   <si>
     <t>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</t>
+  </si>
+  <si>
+    <t>El mes pasado le pusimos pago al 7C lo que era para el 1B</t>
   </si>
 </sst>
 </file>
@@ -735,7 +733,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -802,6 +800,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1214,7 +1218,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1416,12 +1420,6 @@
     <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1467,7 +1465,6 @@
     <xf numFmtId="169" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="24" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1476,18 +1473,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1503,8 +1503,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1521,12 +1542,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1539,24 +1554,15 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1635,9 +1641,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1675,9 +1681,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1710,26 +1716,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1762,26 +1751,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1956,30 +1928,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="181" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
       <c r="E1" s="63"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="64" t="s">
         <v>26</v>
@@ -1988,16 +1960,16 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="184" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="186"/>
-      <c r="D3" s="186"/>
-      <c r="E3" s="187"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="185"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2008,7 +1980,7 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>58</v>
       </c>
@@ -2021,7 +1993,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>59</v>
       </c>
@@ -2032,57 +2004,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="188" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="176" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="188"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="188"/>
-      <c r="C9" s="188"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="205" t="s">
+      <c r="C8" s="176"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="176"/>
+      <c r="C10" s="176"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="186" t="s">
         <v>164</v>
       </c>
-      <c r="B13" s="205"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="205"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="205"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="205"/>
-      <c r="B15" s="205"/>
-      <c r="C15" s="205"/>
-      <c r="D15" s="205"/>
-      <c r="E15" s="205"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="205"/>
-      <c r="B16" s="205"/>
-      <c r="C16" s="205"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="205"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="186"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="186"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="186"/>
+      <c r="B14" s="186"/>
+      <c r="C14" s="186"/>
+      <c r="D14" s="186"/>
+      <c r="E14" s="186"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="186"/>
+      <c r="B15" s="186"/>
+      <c r="C15" s="186"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="186"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="186"/>
+      <c r="B16" s="186"/>
+      <c r="C16" s="186"/>
+      <c r="D16" s="186"/>
+      <c r="E16" s="186"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2091,7 +2063,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>32</v>
       </c>
@@ -2100,11 +2072,11 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="181" t="s">
+    <row r="22" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="177" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="182"/>
+      <c r="B22" s="178"/>
       <c r="C22" s="5"/>
       <c r="D22" s="126">
         <v>803081</v>
@@ -2113,11 +2085,11 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="181" t="s">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="177" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="182"/>
+      <c r="B23" s="178"/>
       <c r="C23" s="5"/>
       <c r="D23" s="126">
         <v>1000830.1</v>
@@ -2126,29 +2098,29 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="141" t="s">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="142"/>
+      <c r="B24" s="117"/>
       <c r="C24" s="5"/>
       <c r="D24" s="126">
         <v>-247705.44</v>
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="141" t="s">
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="B25" s="142"/>
+      <c r="B25" s="117"/>
       <c r="C25" s="5"/>
       <c r="D25" s="126">
         <v>0.34</v>
       </c>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55" t="s">
         <v>33</v>
       </c>
@@ -2161,7 +2133,7 @@
       <c r="E26" s="104"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
@@ -2170,28 +2142,28 @@
       <c r="D27" s="126"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="28"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="126"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="126"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="128"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
@@ -2200,7 +2172,7 @@
       <c r="D31" s="128"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="55" t="s">
         <v>33</v>
       </c>
@@ -2212,7 +2184,7 @@
       </c>
       <c r="E32" s="104"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
         <v>1</v>
       </c>
@@ -2225,7 +2197,7 @@
       </c>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="34" t="s">
         <v>18</v>
       </c>
@@ -2234,7 +2206,7 @@
       <c r="D34" s="131"/>
       <c r="E34" s="106"/>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="179" t="s">
         <v>123</v>
       </c>
@@ -2247,7 +2219,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="179" t="s">
         <v>116</v>
       </c>
@@ -2260,7 +2232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="179" t="s">
         <v>124</v>
       </c>
@@ -2271,7 +2243,7 @@
       </c>
       <c r="E37" s="107"/>
     </row>
-    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
         <v>15</v>
       </c>
@@ -2283,7 +2255,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="34" t="s">
         <v>29</v>
       </c>
@@ -2292,11 +2264,11 @@
       <c r="D39" s="134"/>
       <c r="E39" s="109"/>
     </row>
-    <row r="40" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="181" t="s">
+    <row r="40" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="177" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="182"/>
+      <c r="B40" s="178"/>
       <c r="C40" s="52"/>
       <c r="D40" s="135">
         <v>176994.85</v>
@@ -2305,11 +2277,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="181" t="s">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="177" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="182"/>
+      <c r="B41" s="178"/>
       <c r="C41" s="52"/>
       <c r="D41" s="136">
         <v>15087.23</v>
@@ -2318,7 +2290,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
         <v>2</v>
       </c>
@@ -2330,7 +2302,7 @@
         <v>192082.08000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="34" t="s">
         <v>16</v>
       </c>
@@ -2339,7 +2311,7 @@
       <c r="D43" s="137"/>
       <c r="E43" s="113"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -2353,7 +2325,7 @@
       </c>
       <c r="G44" s="91"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>57</v>
       </c>
@@ -2368,7 +2340,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2385,7 +2357,7 @@
         <v>Transf 12/02</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="str">
         <f>A46</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2402,7 +2374,7 @@
         <v>Transf 12/02</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
         <v>3</v>
       </c>
@@ -2414,7 +2386,7 @@
         <v>701934.34</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="34" t="s">
         <v>17</v>
       </c>
@@ -2423,7 +2395,7 @@
       <c r="D49" s="137"/>
       <c r="E49" s="113"/>
     </row>
-    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>121</v>
       </c>
@@ -2432,11 +2404,11 @@
       <c r="D50" s="138"/>
       <c r="E50" s="118"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="181" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="177" t="s">
         <v>122</v>
       </c>
-      <c r="B51" s="182"/>
+      <c r="B51" s="178"/>
       <c r="C51" s="5"/>
       <c r="D51" s="138">
         <v>817259.26</v>
@@ -2445,7 +2417,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="29" t="s">
         <v>4</v>
       </c>
@@ -2457,14 +2429,14 @@
         <v>817259.26</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="34"/>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
       <c r="D53" s="133"/>
       <c r="E53" s="114"/>
     </row>
-    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="122" t="s">
         <v>61</v>
       </c>
@@ -2477,20 +2449,20 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="122" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="142"/>
+      <c r="B55" s="117"/>
       <c r="C55" s="5"/>
       <c r="D55" s="138">
         <v>60000</v>
       </c>
-      <c r="E55" s="170" t="s">
+      <c r="E55" s="168" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="29" t="s">
         <v>8</v>
       </c>
@@ -2502,7 +2474,7 @@
         <v>235500</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="34" t="s">
         <v>11</v>
       </c>
@@ -2511,7 +2483,7 @@
       <c r="D57" s="130"/>
       <c r="E57" s="114"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>54</v>
       </c>
@@ -2522,7 +2494,7 @@
       </c>
       <c r="E58" s="116"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
@@ -2534,7 +2506,7 @@
       </c>
       <c r="E59" s="39"/>
     </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="50" t="s">
         <v>15</v>
       </c>
@@ -2546,14 +2518,14 @@
         <v>131189.06</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="69"/>
       <c r="E61" s="77"/>
     </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="30" t="s">
         <v>47</v>
       </c>
@@ -2562,13 +2534,13 @@
       <c r="D62" s="78"/>
       <c r="E62" s="79"/>
     </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="D63" s="80"/>
       <c r="E63" s="81"/>
       <c r="F63" s="42"/>
     </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
@@ -2587,7 +2559,7 @@
       <c r="K64" s="91"/>
       <c r="L64" s="91"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D65" s="80"/>
       <c r="E65" s="80"/>
       <c r="H65" s="91"/>
@@ -2596,12 +2568,12 @@
       <c r="K65" s="91"/>
       <c r="L65" s="91"/>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D66" s="80"/>
       <c r="E66" s="80"/>
       <c r="H66" s="124"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>42</v>
       </c>
@@ -2610,35 +2582,35 @@
       <c r="D67" s="84"/>
       <c r="E67" s="85"/>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="181"/>
-      <c r="B68" s="182"/>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="177"/>
+      <c r="B68" s="178"/>
       <c r="C68" s="5"/>
       <c r="D68" s="95"/>
       <c r="E68" s="71"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="181"/>
-      <c r="B69" s="182"/>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="177"/>
+      <c r="B69" s="178"/>
       <c r="C69" s="5"/>
       <c r="D69" s="73"/>
       <c r="E69" s="71"/>
     </row>
-    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="179"/>
       <c r="B70" s="180"/>
       <c r="C70" s="5"/>
       <c r="D70" s="73"/>
       <c r="E70" s="71"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="72"/>
       <c r="B71" s="74"/>
       <c r="C71" s="5"/>
       <c r="D71" s="73"/>
       <c r="E71" s="71"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="48"/>
       <c r="B72" s="47"/>
       <c r="C72" s="47"/>
@@ -2648,19 +2620,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="174" t="s">
+    <row r="73" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="B75" s="175"/>
-      <c r="C75" s="175"/>
-      <c r="D75" s="176"/>
-      <c r="E75" s="177"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="172"/>
+      <c r="C75" s="172"/>
+      <c r="D75" s="173"/>
+      <c r="E75" s="174"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>20</v>
       </c>
@@ -2672,8 +2644,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="67" t="s">
         <v>13</v>
       </c>
@@ -2682,7 +2654,7 @@
         <v>3879170.7400000007</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="67" t="s">
         <v>14</v>
       </c>
@@ -2691,7 +2663,7 @@
         <v>3879170.7400000007</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="67" t="s">
         <v>21</v>
       </c>
@@ -2700,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="67" t="s">
         <v>38</v>
       </c>
@@ -2709,44 +2681,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="184"/>
-      <c r="B85" s="184"/>
-      <c r="C85" s="184"/>
-      <c r="D85" s="184"/>
-      <c r="E85" s="184"/>
-    </row>
-    <row r="86" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="184"/>
-      <c r="B86" s="184"/>
-      <c r="C86" s="184"/>
-      <c r="D86" s="184"/>
-      <c r="E86" s="184"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="184"/>
-      <c r="B87" s="184"/>
-      <c r="C87" s="184"/>
-      <c r="D87" s="184"/>
-      <c r="E87" s="184"/>
-    </row>
-    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="182"/>
+      <c r="B85" s="182"/>
+      <c r="C85" s="182"/>
+      <c r="D85" s="182"/>
+      <c r="E85" s="182"/>
+    </row>
+    <row r="86" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="182"/>
+      <c r="B86" s="182"/>
+      <c r="C86" s="182"/>
+      <c r="D86" s="182"/>
+      <c r="E86" s="182"/>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="182"/>
+      <c r="B87" s="182"/>
+      <c r="C87" s="182"/>
+      <c r="D87" s="182"/>
+      <c r="E87" s="182"/>
+    </row>
+    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B89" s="92"/>
       <c r="C89" s="23"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="32"/>
       <c r="B90" s="57">
         <v>0</v>
       </c>
       <c r="C90" s="25"/>
     </row>
-    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="s">
         <v>7</v>
       </c>
@@ -2756,14 +2728,14 @@
       </c>
       <c r="C91" s="23"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="24"/>
       <c r="B92" s="39">
         <v>0</v>
       </c>
       <c r="C92" s="23"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
         <v>39</v>
       </c>
@@ -2773,19 +2745,19 @@
       </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="27"/>
       <c r="B94" s="46"/>
       <c r="C94" s="23"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="46"/>
       <c r="C95" s="23"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="38" t="s">
         <v>22</v>
       </c>
@@ -2795,7 +2767,7 @@
       </c>
       <c r="C96" s="23"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="27" t="s">
         <v>23</v>
       </c>
@@ -2805,7 +2777,7 @@
       </c>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="31" t="s">
         <v>8</v>
       </c>
@@ -2816,33 +2788,33 @@
       <c r="C98" s="26"/>
       <c r="D98" s="42"/>
     </row>
-    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="40"/>
       <c r="C99" s="26"/>
       <c r="D99" s="42"/>
       <c r="E99" s="93"/>
       <c r="F99" s="94"/>
     </row>
-    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="41"/>
       <c r="C100" s="26"/>
     </row>
-    <row r="101" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101"/>
       <c r="B101" s="40"/>
       <c r="C101" s="36"/>
     </row>
-    <row r="102" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="97" t="s">
         <v>156</v>
       </c>
-      <c r="B102" s="173">
+      <c r="B102" s="170">
         <v>3790829.07</v>
       </c>
       <c r="C102" s="36"/>
       <c r="D102" s="45"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="52" t="s">
         <v>48</v>
       </c>
@@ -2851,7 +2823,7 @@
         <v>-3879170.7400000007</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="52" t="s">
         <v>49</v>
       </c>
@@ -2860,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="52" t="s">
         <v>157</v>
       </c>
@@ -2868,7 +2840,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="52" t="s">
         <v>136</v>
       </c>
@@ -2876,7 +2848,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="52" t="s">
         <v>52</v>
       </c>
@@ -2885,7 +2857,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="52" t="s">
         <v>50</v>
       </c>
@@ -2894,7 +2866,7 @@
         <v>3961860.6800000006</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="99" t="s">
         <v>45</v>
       </c>
@@ -2904,24 +2876,24 @@
       </c>
       <c r="D109" s="42"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="98"/>
       <c r="B110" s="98"/>
     </row>
-    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="185" t="s">
+    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="B112" s="185"/>
-      <c r="C112" s="185"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="185"/>
-      <c r="B113" s="185"/>
-      <c r="C113" s="185"/>
-    </row>
-    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="183"/>
+      <c r="C112" s="183"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="183"/>
+      <c r="B113" s="183"/>
+      <c r="C113" s="183"/>
+    </row>
+    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="87" t="s">
         <v>155</v>
       </c>
@@ -2933,13 +2905,13 @@
       </c>
       <c r="E114" s="103"/>
     </row>
-    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="87"/>
       <c r="B115" s="89"/>
       <c r="C115" s="86"/>
       <c r="D115" s="103"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="43" t="s">
         <v>8</v>
       </c>
@@ -2949,55 +2921,55 @@
       </c>
       <c r="C116" s="44"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M117" s="7"/>
     </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="184"/>
-      <c r="B118" s="184"/>
-      <c r="C118" s="184"/>
-      <c r="D118" s="184"/>
-      <c r="E118" s="184"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="184"/>
-      <c r="B119" s="184"/>
-      <c r="C119" s="184"/>
-      <c r="D119" s="184"/>
-      <c r="E119" s="184"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="184"/>
-      <c r="B120" s="184"/>
-      <c r="C120" s="184"/>
-      <c r="D120" s="184"/>
-      <c r="E120" s="184"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="184"/>
-      <c r="B121" s="184"/>
-      <c r="C121" s="184"/>
-      <c r="D121" s="184"/>
-      <c r="E121" s="184"/>
+    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="182"/>
+      <c r="B118" s="182"/>
+      <c r="C118" s="182"/>
+      <c r="D118" s="182"/>
+      <c r="E118" s="182"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="182"/>
+      <c r="B119" s="182"/>
+      <c r="C119" s="182"/>
+      <c r="D119" s="182"/>
+      <c r="E119" s="182"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="182"/>
+      <c r="B120" s="182"/>
+      <c r="C120" s="182"/>
+      <c r="D120" s="182"/>
+      <c r="E120" s="182"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="182"/>
+      <c r="B121" s="182"/>
+      <c r="C121" s="182"/>
+      <c r="D121" s="182"/>
+      <c r="E121" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A118:E121"/>
     <mergeCell ref="A112:C113"/>
     <mergeCell ref="A85:E87"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
   </mergeCells>
@@ -3010,42 +2982,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="191"/>
-      <c r="F1" s="191"/>
-      <c r="G1" s="191"/>
-      <c r="H1" s="191"/>
-      <c r="I1" s="191"/>
-      <c r="J1" s="191"/>
-      <c r="K1" s="191"/>
-      <c r="L1" s="191"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3062,14 +3034,14 @@
       <c r="J2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="178">
+      <c r="K2" s="175">
         <v>3155000</v>
       </c>
       <c r="L2" s="96"/>
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3084,109 +3056,109 @@
       <c r="L3" s="54"/>
       <c r="M3" s="58"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="194" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="187" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="194" t="s">
+      <c r="D4" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="194" t="s">
+      <c r="E4" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="192" t="s">
+      <c r="F4" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="194" t="s">
+      <c r="G4" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="196" t="s">
+      <c r="H4" s="199" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="192" t="s">
+      <c r="I4" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="192" t="s">
+      <c r="J4" s="197" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="198" t="s">
+      <c r="K4" s="201" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="189" t="s">
+      <c r="M4" s="194" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="195"/>
-      <c r="B5" s="200"/>
-      <c r="C5" s="195"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="193"/>
-      <c r="G5" s="195"/>
-      <c r="H5" s="197"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
-      <c r="K5" s="199"/>
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="189"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="202"/>
       <c r="L5" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/03</v>
       </c>
-      <c r="M5" s="190"/>
-    </row>
-    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="143">
+      <c r="M5" s="195"/>
+    </row>
+    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="141">
         <v>1</v>
       </c>
-      <c r="B6" s="143" t="s">
+      <c r="B6" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="143" t="s">
+      <c r="C6" s="141" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="143" t="s">
+      <c r="D6" s="141" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="168">
+      <c r="E6" s="166">
         <v>3.43</v>
       </c>
-      <c r="F6" s="145">
+      <c r="F6" s="143">
         <v>164698.01</v>
       </c>
-      <c r="G6" s="154">
+      <c r="G6" s="152">
         <f>F6</f>
         <v>164698.01</v>
       </c>
-      <c r="H6" s="146">
+      <c r="H6" s="144">
         <f t="shared" ref="H6:H30" si="0">F6-G6</f>
         <v>0</v>
       </c>
-      <c r="I6" s="146">
+      <c r="I6" s="144">
         <f>IF(H6&gt;0,H6*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="147">
+      <c r="J6" s="145">
         <f>K$2*E6%</f>
         <v>108216.50000000001</v>
       </c>
-      <c r="K6" s="148">
+      <c r="K6" s="146">
         <f>G$2*E6/100</f>
         <v>27491.45</v>
       </c>
-      <c r="L6" s="149">
+      <c r="L6" s="147">
         <f t="shared" ref="L6:L30" si="1">ROUND(SUM(H6:K6),0) + N6</f>
         <v>135708.01</v>
       </c>
-      <c r="M6" s="150">
+      <c r="M6" s="148">
         <f t="shared" ref="M6:M30" si="2">ROUND(L6*3%,0) + L6</f>
         <v>139779.01</v>
       </c>
@@ -3194,48 +3166,48 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="143">
+    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="203">
         <f>A6+1</f>
         <v>2</v>
       </c>
-      <c r="B7" s="143" t="s">
+      <c r="B7" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="143" t="s">
+      <c r="C7" s="203" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="151" t="s">
+      <c r="D7" s="204" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="168">
+      <c r="E7" s="205">
         <v>2.95</v>
       </c>
-      <c r="F7" s="145">
+      <c r="F7" s="206">
         <v>141651.01999999999</v>
       </c>
-      <c r="G7" s="154"/>
-      <c r="H7" s="146">
+      <c r="G7" s="152"/>
+      <c r="H7" s="144">
         <f t="shared" si="0"/>
         <v>141651.01999999999</v>
       </c>
-      <c r="I7" s="146">
+      <c r="I7" s="144">
         <f t="shared" ref="I7:I30" si="3">IF(H7&gt;0,H7*3%,0)</f>
         <v>4249.5305999999991</v>
       </c>
-      <c r="J7" s="147">
+      <c r="J7" s="145">
         <f t="shared" ref="J7:J29" si="4">K$2*E7%</f>
         <v>93072.5</v>
       </c>
-      <c r="K7" s="148">
+      <c r="K7" s="146">
         <f t="shared" ref="K7:K29" si="5">G$2*E7/100</f>
         <v>23644.25</v>
       </c>
-      <c r="L7" s="149">
+      <c r="L7" s="147">
         <f t="shared" si="1"/>
         <v>262617.02</v>
       </c>
-      <c r="M7" s="150">
+      <c r="M7" s="148">
         <f t="shared" si="2"/>
         <v>270496.02</v>
       </c>
@@ -3245,52 +3217,52 @@
       </c>
       <c r="O7" s="42"/>
     </row>
-    <row r="8" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="152">
+    <row r="8" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="150">
         <f t="shared" ref="A8:A29" si="6">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="152" t="s">
+      <c r="C8" s="150" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="153" t="s">
+      <c r="D8" s="151" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="169">
+      <c r="E8" s="167">
         <f>5.78+1.02</f>
         <v>6.8000000000000007</v>
       </c>
-      <c r="F8" s="154">
+      <c r="F8" s="152">
         <v>326517.03000000003</v>
       </c>
-      <c r="G8" s="154">
+      <c r="G8" s="152">
         <f>F8</f>
         <v>326517.03000000003</v>
       </c>
-      <c r="H8" s="146">
+      <c r="H8" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="146">
+      <c r="I8" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J8" s="147">
+      <c r="J8" s="145">
         <f t="shared" si="4"/>
         <v>214540.00000000003</v>
       </c>
-      <c r="K8" s="148">
+      <c r="K8" s="146">
         <f t="shared" si="5"/>
         <v>54502.000000000007</v>
       </c>
-      <c r="L8" s="149">
+      <c r="L8" s="147">
         <f t="shared" si="1"/>
         <v>269042.03000000003</v>
       </c>
-      <c r="M8" s="150">
+      <c r="M8" s="148">
         <f t="shared" si="2"/>
         <v>277113.03000000003</v>
       </c>
@@ -3302,51 +3274,51 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="143">
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="141">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="141" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="143" t="s">
+      <c r="C9" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="151" t="s">
+      <c r="D9" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="168">
+      <c r="E9" s="166">
         <v>3.43</v>
       </c>
-      <c r="F9" s="145">
+      <c r="F9" s="143">
         <v>164699.04</v>
       </c>
-      <c r="G9" s="154">
+      <c r="G9" s="152">
         <f>F9</f>
         <v>164699.04</v>
       </c>
-      <c r="H9" s="146">
+      <c r="H9" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="146">
+      <c r="I9" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J9" s="147">
+      <c r="J9" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K9" s="148">
+      <c r="K9" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L9" s="149">
+      <c r="L9" s="147">
         <f t="shared" si="1"/>
         <v>135708.04</v>
       </c>
-      <c r="M9" s="150">
+      <c r="M9" s="148">
         <f t="shared" si="2"/>
         <v>139779.04</v>
       </c>
@@ -3356,49 +3328,49 @@
       </c>
       <c r="P9" s="42"/>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="143">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="141">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="B10" s="143" t="s">
+      <c r="B10" s="141" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="143" t="s">
+      <c r="C10" s="141" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="151"/>
-      <c r="E10" s="168">
+      <c r="D10" s="149"/>
+      <c r="E10" s="166">
         <v>2.95</v>
       </c>
-      <c r="F10" s="145">
+      <c r="F10" s="143">
         <v>141651.04999999999</v>
       </c>
-      <c r="G10" s="154">
+      <c r="G10" s="152">
         <f>F10</f>
         <v>141651.04999999999</v>
       </c>
-      <c r="H10" s="146">
+      <c r="H10" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="146">
+      <c r="I10" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J10" s="147">
+      <c r="J10" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K10" s="148">
+      <c r="K10" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L10" s="149">
+      <c r="L10" s="147">
         <f t="shared" si="1"/>
         <v>116717.05</v>
       </c>
-      <c r="M10" s="150">
+      <c r="M10" s="148">
         <f t="shared" si="2"/>
         <v>120219.05</v>
       </c>
@@ -3408,51 +3380,51 @@
       </c>
       <c r="P10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="143">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="141">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="143" t="s">
+      <c r="C11" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="143" t="s">
+      <c r="D11" s="141" t="s">
         <v>138</v>
       </c>
-      <c r="E11" s="168">
+      <c r="E11" s="166">
         <v>5.69</v>
       </c>
-      <c r="F11" s="145">
+      <c r="F11" s="143">
         <v>273218.06</v>
       </c>
-      <c r="G11" s="154">
+      <c r="G11" s="152">
         <f>F11</f>
         <v>273218.06</v>
       </c>
-      <c r="H11" s="146">
+      <c r="H11" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="146">
+      <c r="I11" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J11" s="147">
+      <c r="J11" s="145">
         <f t="shared" si="4"/>
         <v>179519.50000000003</v>
       </c>
-      <c r="K11" s="148">
+      <c r="K11" s="146">
         <f t="shared" si="5"/>
         <v>45605.35</v>
       </c>
-      <c r="L11" s="149">
+      <c r="L11" s="147">
         <f t="shared" si="1"/>
         <v>225125.06</v>
       </c>
-      <c r="M11" s="150">
+      <c r="M11" s="148">
         <f t="shared" si="2"/>
         <v>231879.06</v>
       </c>
@@ -3461,49 +3433,49 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="143">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="141">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="B12" s="143" t="s">
+      <c r="B12" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="143" t="s">
+      <c r="C12" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="143"/>
-      <c r="E12" s="168">
+      <c r="D12" s="141"/>
+      <c r="E12" s="166">
         <v>3.43</v>
       </c>
-      <c r="F12" s="145">
+      <c r="F12" s="143">
         <v>164699.07</v>
       </c>
-      <c r="G12" s="154">
+      <c r="G12" s="152">
         <f>F12</f>
         <v>164699.07</v>
       </c>
-      <c r="H12" s="146">
+      <c r="H12" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="146">
+      <c r="I12" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J12" s="147">
+      <c r="J12" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K12" s="148">
+      <c r="K12" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L12" s="149">
+      <c r="L12" s="147">
         <f t="shared" si="1"/>
         <v>135708.07</v>
       </c>
-      <c r="M12" s="150">
+      <c r="M12" s="148">
         <f t="shared" si="2"/>
         <v>139779.07</v>
       </c>
@@ -3512,46 +3484,46 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="143">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="141">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="B13" s="143" t="s">
+      <c r="B13" s="141" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="143" t="s">
+      <c r="C13" s="141" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="151"/>
-      <c r="E13" s="168">
+      <c r="D13" s="149"/>
+      <c r="E13" s="166">
         <v>2.95</v>
       </c>
-      <c r="F13" s="145">
+      <c r="F13" s="143">
         <v>141651.07999999999</v>
       </c>
-      <c r="G13" s="154"/>
-      <c r="H13" s="146">
+      <c r="G13" s="152"/>
+      <c r="H13" s="144">
         <f t="shared" si="0"/>
         <v>141651.07999999999</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="144">
         <f t="shared" si="3"/>
         <v>4249.5323999999991</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="147">
         <f t="shared" si="1"/>
         <v>262617.08</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="148">
         <f t="shared" si="2"/>
         <v>270496.08</v>
       </c>
@@ -3560,51 +3532,51 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="143">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="141">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="B14" s="143" t="s">
+      <c r="B14" s="141" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="143" t="s">
+      <c r="C14" s="141" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="151" t="s">
+      <c r="D14" s="149" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="168">
+      <c r="E14" s="166">
         <v>5.69</v>
       </c>
-      <c r="F14" s="145">
+      <c r="F14" s="143">
         <v>273218.09000000003</v>
       </c>
-      <c r="G14" s="154">
+      <c r="G14" s="152">
         <f>F14</f>
         <v>273218.09000000003</v>
       </c>
-      <c r="H14" s="146">
+      <c r="H14" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="147">
+      <c r="J14" s="145">
         <f t="shared" si="4"/>
         <v>179519.50000000003</v>
       </c>
-      <c r="K14" s="148">
+      <c r="K14" s="146">
         <f t="shared" si="5"/>
         <v>45605.35</v>
       </c>
-      <c r="L14" s="149">
+      <c r="L14" s="147">
         <f t="shared" si="1"/>
         <v>225125.09</v>
       </c>
-      <c r="M14" s="150">
+      <c r="M14" s="148">
         <f t="shared" si="2"/>
         <v>231879.09</v>
       </c>
@@ -3613,50 +3585,50 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="143">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="141">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="B15" s="143" t="s">
+      <c r="B15" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="143" t="s">
+      <c r="C15" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="149" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="168">
+      <c r="E15" s="166">
         <v>3.43</v>
       </c>
-      <c r="F15" s="145">
+      <c r="F15" s="143">
         <v>405721.1</v>
       </c>
-      <c r="G15" s="154">
+      <c r="G15" s="152">
         <v>406000</v>
       </c>
-      <c r="H15" s="146">
+      <c r="H15" s="144">
         <f t="shared" si="0"/>
         <v>-278.90000000002328</v>
       </c>
-      <c r="I15" s="146">
+      <c r="I15" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="147">
+      <c r="J15" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K15" s="148">
+      <c r="K15" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L15" s="149">
+      <c r="L15" s="147">
         <f t="shared" si="1"/>
         <v>135429.1</v>
       </c>
-      <c r="M15" s="150">
+      <c r="M15" s="148">
         <f t="shared" si="2"/>
         <v>139492.1</v>
       </c>
@@ -3665,51 +3637,51 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="143">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="141">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="B16" s="143" t="s">
+      <c r="B16" s="141" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="143" t="s">
+      <c r="C16" s="141" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="151" t="s">
+      <c r="D16" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="E16" s="168">
+      <c r="E16" s="166">
         <v>2.95</v>
       </c>
-      <c r="F16" s="145">
+      <c r="F16" s="143">
         <v>141651.10999999999</v>
       </c>
-      <c r="G16" s="154">
+      <c r="G16" s="152">
         <f>F16</f>
         <v>141651.10999999999</v>
       </c>
-      <c r="H16" s="146">
+      <c r="H16" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="146">
+      <c r="I16" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="147">
+      <c r="J16" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K16" s="148">
+      <c r="K16" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L16" s="149">
+      <c r="L16" s="147">
         <f t="shared" si="1"/>
         <v>116717.11</v>
       </c>
-      <c r="M16" s="150">
+      <c r="M16" s="148">
         <f t="shared" si="2"/>
         <v>120219.11</v>
       </c>
@@ -3718,52 +3690,52 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="143">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="141">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="B17" s="143" t="s">
+      <c r="B17" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="143" t="s">
+      <c r="C17" s="141" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="151" t="s">
+      <c r="D17" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="E17" s="168">
+      <c r="E17" s="166">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F17" s="145">
+      <c r="F17" s="143">
         <v>297707.12</v>
       </c>
-      <c r="G17" s="154">
+      <c r="G17" s="152">
         <f>F17</f>
         <v>297707.12</v>
       </c>
-      <c r="H17" s="146">
+      <c r="H17" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I17" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="147">
+      <c r="J17" s="145">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K17" s="148">
+      <c r="K17" s="146">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L17" s="149">
+      <c r="L17" s="147">
         <f t="shared" si="1"/>
         <v>245303.12</v>
       </c>
-      <c r="M17" s="150">
+      <c r="M17" s="148">
         <f t="shared" si="2"/>
         <v>252662.12</v>
       </c>
@@ -3772,51 +3744,51 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="143">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="141">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="B18" s="143" t="s">
+      <c r="B18" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="141" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="151" t="s">
+      <c r="D18" s="149" t="s">
         <v>158</v>
       </c>
-      <c r="E18" s="168">
+      <c r="E18" s="166">
         <v>3.43</v>
       </c>
-      <c r="F18" s="145">
+      <c r="F18" s="143">
         <v>164699.13</v>
       </c>
-      <c r="G18" s="154">
+      <c r="G18" s="152">
         <f>F18</f>
         <v>164699.13</v>
       </c>
-      <c r="H18" s="146">
+      <c r="H18" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="146">
+      <c r="I18" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="147">
+      <c r="J18" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K18" s="148">
+      <c r="K18" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L18" s="149">
+      <c r="L18" s="147">
         <f t="shared" si="1"/>
         <v>135708.13</v>
       </c>
-      <c r="M18" s="150">
+      <c r="M18" s="148">
         <f t="shared" si="2"/>
         <v>139779.13</v>
       </c>
@@ -3825,49 +3797,49 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="143">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="141">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="B19" s="143" t="s">
+      <c r="B19" s="141" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="143" t="s">
+      <c r="C19" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="151"/>
-      <c r="E19" s="168">
+      <c r="D19" s="149"/>
+      <c r="E19" s="166">
         <v>2.95</v>
       </c>
-      <c r="F19" s="145">
+      <c r="F19" s="143">
         <v>141650.14000000001</v>
       </c>
-      <c r="G19" s="154">
+      <c r="G19" s="152">
         <f>F19</f>
         <v>141650.14000000001</v>
       </c>
-      <c r="H19" s="146">
+      <c r="H19" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="146">
+      <c r="I19" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="147">
+      <c r="J19" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K19" s="148">
+      <c r="K19" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L19" s="149">
+      <c r="L19" s="147">
         <f t="shared" si="1"/>
         <v>116717.14</v>
       </c>
-      <c r="M19" s="150">
+      <c r="M19" s="148">
         <f t="shared" si="2"/>
         <v>120219.14</v>
       </c>
@@ -3876,49 +3848,49 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="152">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="150">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="B20" s="152" t="s">
+      <c r="B20" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="152" t="s">
+      <c r="C20" s="150" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="153" t="s">
+      <c r="D20" s="151" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="169">
+      <c r="E20" s="167">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F20" s="154">
+      <c r="F20" s="152">
         <v>297707.15000000002</v>
       </c>
-      <c r="G20" s="154"/>
-      <c r="H20" s="146">
+      <c r="G20" s="152"/>
+      <c r="H20" s="144">
         <f t="shared" si="0"/>
         <v>297707.15000000002</v>
       </c>
-      <c r="I20" s="146">
+      <c r="I20" s="144">
         <f t="shared" si="3"/>
         <v>8931.2145</v>
       </c>
-      <c r="J20" s="147">
+      <c r="J20" s="145">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K20" s="148">
+      <c r="K20" s="146">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L20" s="149">
+      <c r="L20" s="147">
         <f t="shared" si="1"/>
         <v>551941.15</v>
       </c>
-      <c r="M20" s="150">
+      <c r="M20" s="148">
         <f t="shared" si="2"/>
         <v>568499.15</v>
       </c>
@@ -3927,49 +3899,49 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="143">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="141">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="B21" s="143" t="s">
+      <c r="B21" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="143" t="s">
+      <c r="C21" s="141" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="143"/>
-      <c r="E21" s="168">
+      <c r="D21" s="141"/>
+      <c r="E21" s="166">
         <v>3.43</v>
       </c>
-      <c r="F21" s="145">
+      <c r="F21" s="143">
         <v>164699.16</v>
       </c>
-      <c r="G21" s="154">
+      <c r="G21" s="152">
         <f>F21</f>
         <v>164699.16</v>
       </c>
-      <c r="H21" s="146">
+      <c r="H21" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="146">
+      <c r="I21" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="147">
+      <c r="J21" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K21" s="148">
+      <c r="K21" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L21" s="149">
+      <c r="L21" s="147">
         <f t="shared" si="1"/>
         <v>135708.16</v>
       </c>
-      <c r="M21" s="150">
+      <c r="M21" s="148">
         <f t="shared" si="2"/>
         <v>139779.16</v>
       </c>
@@ -3978,48 +3950,48 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="143">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="141">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="B22" s="143" t="s">
+      <c r="B22" s="141" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="143" t="s">
+      <c r="C22" s="141" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="151" t="s">
+      <c r="D22" s="149" t="s">
         <v>144</v>
       </c>
-      <c r="E22" s="168">
+      <c r="E22" s="166">
         <v>2.95</v>
       </c>
-      <c r="F22" s="154">
+      <c r="F22" s="152">
         <v>141651.17000000001</v>
       </c>
-      <c r="G22" s="154"/>
-      <c r="H22" s="146">
+      <c r="G22" s="152"/>
+      <c r="H22" s="144">
         <f t="shared" si="0"/>
         <v>141651.17000000001</v>
       </c>
-      <c r="I22" s="146">
+      <c r="I22" s="144">
         <f t="shared" si="3"/>
         <v>4249.5351000000001</v>
       </c>
-      <c r="J22" s="147">
+      <c r="J22" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K22" s="148">
+      <c r="K22" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L22" s="149">
+      <c r="L22" s="147">
         <f t="shared" si="1"/>
         <v>262617.17</v>
       </c>
-      <c r="M22" s="150">
+      <c r="M22" s="148">
         <f t="shared" si="2"/>
         <v>270496.17</v>
       </c>
@@ -4028,50 +4000,50 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="143">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="141">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="B23" s="143" t="s">
+      <c r="B23" s="141" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="143" t="s">
+      <c r="C23" s="141" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="155"/>
-      <c r="E23" s="168">
+      <c r="D23" s="153"/>
+      <c r="E23" s="166">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F23" s="145">
+      <c r="F23" s="143">
         <v>297707.18</v>
       </c>
-      <c r="G23" s="154">
+      <c r="G23" s="152">
         <f>F23</f>
         <v>297707.18</v>
       </c>
-      <c r="H23" s="146">
+      <c r="H23" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="146">
+      <c r="I23" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="147">
+      <c r="J23" s="145">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K23" s="148">
+      <c r="K23" s="146">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L23" s="149">
+      <c r="L23" s="147">
         <f t="shared" si="1"/>
         <v>245303.18</v>
       </c>
-      <c r="M23" s="150">
+      <c r="M23" s="148">
         <f t="shared" si="2"/>
         <v>252662.18</v>
       </c>
@@ -4080,50 +4052,50 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="143">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="203">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="B24" s="143" t="s">
+      <c r="B24" s="203" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="143" t="s">
+      <c r="C24" s="203" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="151" t="s">
+      <c r="D24" s="204" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="168">
+      <c r="E24" s="205">
         <v>3.43</v>
       </c>
-      <c r="F24" s="145">
+      <c r="F24" s="206">
         <v>154699.19</v>
       </c>
-      <c r="G24" s="172">
+      <c r="G24" s="207">
         <v>141652</v>
       </c>
-      <c r="H24" s="146">
+      <c r="H24" s="144">
         <f t="shared" si="0"/>
         <v>13047.190000000002</v>
       </c>
-      <c r="I24" s="146">
+      <c r="I24" s="144">
         <f t="shared" si="3"/>
         <v>391.41570000000007</v>
       </c>
-      <c r="J24" s="147">
+      <c r="J24" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K24" s="148">
+      <c r="K24" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L24" s="149">
+      <c r="L24" s="147">
         <f t="shared" si="1"/>
         <v>149147.19</v>
       </c>
-      <c r="M24" s="150">
+      <c r="M24" s="148">
         <f t="shared" si="2"/>
         <v>153621.19</v>
       </c>
@@ -4132,50 +4104,50 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="143">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="141">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="B25" s="156" t="s">
+      <c r="B25" s="154" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="143" t="s">
+      <c r="C25" s="141" t="s">
         <v>145</v>
       </c>
-      <c r="D25" s="151" t="s">
+      <c r="D25" s="149" t="s">
         <v>153</v>
       </c>
-      <c r="E25" s="168">
+      <c r="E25" s="166">
         <v>2.95</v>
       </c>
-      <c r="F25" s="157">
+      <c r="F25" s="155">
         <v>141651.20000000001</v>
       </c>
-      <c r="G25" s="158">
+      <c r="G25" s="156">
         <v>141650</v>
       </c>
-      <c r="H25" s="146">
+      <c r="H25" s="144">
         <f t="shared" si="0"/>
         <v>1.2000000000116415</v>
       </c>
-      <c r="I25" s="146">
+      <c r="I25" s="144">
         <f t="shared" si="3"/>
         <v>3.6000000000349246E-2</v>
       </c>
-      <c r="J25" s="147">
+      <c r="J25" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K25" s="148">
+      <c r="K25" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L25" s="149">
+      <c r="L25" s="147">
         <f t="shared" si="1"/>
         <v>116718.2</v>
       </c>
-      <c r="M25" s="150">
+      <c r="M25" s="148">
         <f t="shared" si="2"/>
         <v>120220.2</v>
       </c>
@@ -4184,47 +4156,47 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="143">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="141">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="B26" s="156" t="s">
+      <c r="B26" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="159" t="s">
+      <c r="C26" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="151"/>
-      <c r="E26" s="168">
+      <c r="D26" s="149"/>
+      <c r="E26" s="166">
         <f>5.69+0.51</f>
         <v>6.2</v>
       </c>
-      <c r="F26" s="157">
+      <c r="F26" s="155">
         <v>297707.21000000002</v>
       </c>
-      <c r="G26" s="158"/>
-      <c r="H26" s="146">
+      <c r="G26" s="156"/>
+      <c r="H26" s="144">
         <f t="shared" si="0"/>
         <v>297707.21000000002</v>
       </c>
-      <c r="I26" s="146">
+      <c r="I26" s="144">
         <f t="shared" si="3"/>
         <v>8931.2163</v>
       </c>
-      <c r="J26" s="147">
+      <c r="J26" s="145">
         <f t="shared" si="4"/>
         <v>195610</v>
       </c>
-      <c r="K26" s="148">
+      <c r="K26" s="146">
         <f t="shared" si="5"/>
         <v>49693</v>
       </c>
-      <c r="L26" s="149">
+      <c r="L26" s="147">
         <f t="shared" si="1"/>
         <v>551941.21</v>
       </c>
-      <c r="M26" s="150">
+      <c r="M26" s="148">
         <f t="shared" si="2"/>
         <v>568499.21</v>
       </c>
@@ -4233,50 +4205,50 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="143">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="141">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="B27" s="160" t="s">
+      <c r="B27" s="158" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="143" t="s">
+      <c r="C27" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="151" t="s">
+      <c r="D27" s="149" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="168">
+      <c r="E27" s="166">
         <v>3.43</v>
       </c>
-      <c r="F27" s="157">
+      <c r="F27" s="155">
         <v>164358.22</v>
       </c>
-      <c r="G27" s="158">
+      <c r="G27" s="156">
         <v>165000</v>
       </c>
-      <c r="H27" s="146">
+      <c r="H27" s="144">
         <f t="shared" si="0"/>
         <v>-641.77999999999884</v>
       </c>
-      <c r="I27" s="146">
+      <c r="I27" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="147">
+      <c r="J27" s="145">
         <f t="shared" si="4"/>
         <v>108216.50000000001</v>
       </c>
-      <c r="K27" s="148">
+      <c r="K27" s="146">
         <f t="shared" si="5"/>
         <v>27491.45</v>
       </c>
-      <c r="L27" s="149">
+      <c r="L27" s="147">
         <f t="shared" si="1"/>
         <v>135066.22</v>
       </c>
-      <c r="M27" s="150">
+      <c r="M27" s="148">
         <f t="shared" si="2"/>
         <v>139118.22</v>
       </c>
@@ -4285,48 +4257,48 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="143">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="141">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B28" s="160" t="s">
+      <c r="B28" s="158" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="161" t="s">
+      <c r="C28" s="159" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="162" t="s">
+      <c r="D28" s="160" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="168">
+      <c r="E28" s="166">
         <v>2.95</v>
       </c>
-      <c r="F28" s="157">
+      <c r="F28" s="155">
         <v>141651.23000000001</v>
       </c>
-      <c r="G28" s="158"/>
-      <c r="H28" s="146">
+      <c r="G28" s="156"/>
+      <c r="H28" s="144">
         <f t="shared" si="0"/>
         <v>141651.23000000001</v>
       </c>
-      <c r="I28" s="146">
+      <c r="I28" s="144">
         <f t="shared" si="3"/>
         <v>4249.5369000000001</v>
       </c>
-      <c r="J28" s="147">
+      <c r="J28" s="145">
         <f t="shared" si="4"/>
         <v>93072.5</v>
       </c>
-      <c r="K28" s="148">
+      <c r="K28" s="146">
         <f t="shared" si="5"/>
         <v>23644.25</v>
       </c>
-      <c r="L28" s="149">
+      <c r="L28" s="147">
         <f t="shared" si="1"/>
         <v>262618.23</v>
       </c>
-      <c r="M28" s="150">
+      <c r="M28" s="148">
         <f t="shared" si="2"/>
         <v>270497.23</v>
       </c>
@@ -4335,49 +4307,49 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="143">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="141">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="B29" s="160" t="s">
+      <c r="B29" s="158" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="161" t="s">
+      <c r="C29" s="159" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="162"/>
-      <c r="E29" s="168">
+      <c r="D29" s="160"/>
+      <c r="E29" s="166">
         <v>5.68</v>
       </c>
-      <c r="F29" s="157">
+      <c r="F29" s="155">
         <v>272738.24</v>
       </c>
-      <c r="G29" s="158">
+      <c r="G29" s="156">
         <f>F29</f>
         <v>272738.24</v>
       </c>
-      <c r="H29" s="146">
+      <c r="H29" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="146">
+      <c r="I29" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="147">
+      <c r="J29" s="145">
         <f t="shared" si="4"/>
         <v>179204</v>
       </c>
-      <c r="K29" s="148">
+      <c r="K29" s="146">
         <f t="shared" si="5"/>
         <v>45525.2</v>
       </c>
-      <c r="L29" s="149">
+      <c r="L29" s="147">
         <f t="shared" si="1"/>
         <v>224729.24</v>
       </c>
-      <c r="M29" s="150">
+      <c r="M29" s="148">
         <f t="shared" si="2"/>
         <v>231471.24</v>
       </c>
@@ -4386,43 +4358,43 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="201" t="s">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="190" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="202"/>
-      <c r="C30" s="161" t="s">
+      <c r="B30" s="191"/>
+      <c r="C30" s="159" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="161"/>
-      <c r="E30" s="144"/>
-      <c r="F30" s="157">
+      <c r="D30" s="159"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="155">
         <v>118006.25</v>
       </c>
-      <c r="G30" s="158">
+      <c r="G30" s="156">
         <v>118006.25</v>
       </c>
-      <c r="H30" s="146">
+      <c r="H30" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="146">
+      <c r="I30" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="147">
+      <c r="J30" s="145">
         <f>J13</f>
         <v>93072.5</v>
       </c>
-      <c r="K30" s="148">
+      <c r="K30" s="146">
         <f>K13</f>
         <v>23644.25</v>
       </c>
-      <c r="L30" s="149">
+      <c r="L30" s="147">
         <f t="shared" si="1"/>
         <v>116717.25</v>
       </c>
-      <c r="M30" s="150">
+      <c r="M30" s="148">
         <f t="shared" si="2"/>
         <v>120219.25</v>
       </c>
@@ -4434,132 +4406,140 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="203" t="s">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="192" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="203"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="171">
+      <c r="B31" s="192"/>
+      <c r="C31" s="193"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="169">
         <f>SUM(E6:E30)</f>
         <v>99.700000000000045</v>
       </c>
-      <c r="F31" s="164">
+      <c r="F31" s="162">
         <f t="shared" ref="F31:K31" si="8">SUM(F6:F30)</f>
         <v>5136007.2500000009</v>
       </c>
-      <c r="G31" s="165">
+      <c r="G31" s="163">
         <f t="shared" si="8"/>
         <v>3961860.6800000006</v>
       </c>
-      <c r="H31" s="165">
+      <c r="H31" s="163">
         <f t="shared" si="8"/>
         <v>1174146.5699999998</v>
       </c>
-      <c r="I31" s="165">
+      <c r="I31" s="163">
         <f t="shared" si="8"/>
         <v>35252.017500000002</v>
       </c>
-      <c r="J31" s="166">
+      <c r="J31" s="164">
         <f t="shared" si="8"/>
         <v>3238607.5</v>
       </c>
-      <c r="K31" s="165">
+      <c r="K31" s="163">
         <f t="shared" si="8"/>
         <v>822739.74999999988</v>
       </c>
-      <c r="L31" s="167">
+      <c r="L31" s="165">
         <f>SUM(L6:L23)</f>
         <v>3713811.7100000009</v>
       </c>
-      <c r="M31" s="167">
+      <c r="M31" s="165">
         <f>SUM(M6:M30)</f>
         <v>5428874.25</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="49"/>
       <c r="D32" s="49"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="184" t="str">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="3:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="182" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="184"/>
-      <c r="G34" s="184"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="184"/>
-      <c r="J34" s="184"/>
-      <c r="K34" s="184"/>
-      <c r="L34" s="184"/>
-    </row>
-    <row r="35" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="184"/>
-      <c r="G35" s="184"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="184"/>
-      <c r="J35" s="184"/>
-      <c r="K35" s="184"/>
-      <c r="L35" s="184"/>
-    </row>
-    <row r="36" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="184"/>
-      <c r="G36" s="184"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="184"/>
-      <c r="J36" s="184"/>
-      <c r="K36" s="184"/>
-      <c r="L36" s="184"/>
-    </row>
-    <row r="37" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="184"/>
-      <c r="L37" s="184"/>
-    </row>
-    <row r="38" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="184"/>
-      <c r="G38" s="184"/>
-      <c r="H38" s="184"/>
-      <c r="I38" s="184"/>
-      <c r="J38" s="184"/>
-      <c r="K38" s="184"/>
-      <c r="L38" s="184"/>
-    </row>
-    <row r="39" spans="3:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="184"/>
-      <c r="G39" s="184"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="184"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="184"/>
-      <c r="L39" s="184"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="182"/>
+      <c r="F34" s="182"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="182"/>
+      <c r="I34" s="182"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="182"/>
+      <c r="L34" s="182"/>
+    </row>
+    <row r="35" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="182"/>
+      <c r="D35" s="182"/>
+      <c r="E35" s="182"/>
+      <c r="F35" s="182"/>
+      <c r="G35" s="182"/>
+      <c r="H35" s="182"/>
+      <c r="I35" s="182"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="182"/>
+      <c r="L35" s="182"/>
+    </row>
+    <row r="36" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="182"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="182"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="182"/>
+      <c r="I36" s="182"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="182"/>
+      <c r="L36" s="182"/>
+    </row>
+    <row r="37" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="182"/>
+      <c r="D37" s="182"/>
+      <c r="E37" s="182"/>
+      <c r="F37" s="182"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="182"/>
+      <c r="I37" s="182"/>
+      <c r="J37" s="182"/>
+      <c r="K37" s="182"/>
+      <c r="L37" s="182"/>
+    </row>
+    <row r="38" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="182"/>
+      <c r="D38" s="182"/>
+      <c r="E38" s="182"/>
+      <c r="F38" s="182"/>
+      <c r="G38" s="182"/>
+      <c r="H38" s="182"/>
+      <c r="I38" s="182"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="182"/>
+      <c r="L38" s="182"/>
+    </row>
+    <row r="39" spans="3:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="182"/>
+      <c r="D39" s="182"/>
+      <c r="E39" s="182"/>
+      <c r="F39" s="182"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="182"/>
+      <c r="I39" s="182"/>
+      <c r="J39" s="182"/>
+      <c r="K39" s="182"/>
+      <c r="L39" s="182"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="C34:L39"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="A4:A5"/>
@@ -4568,14 +4548,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4584,9 +4556,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/ANATOLE FRANCE/FEBRERO/ANATOLE-Febrero.xlsx
+++ b/2026/ANATOLE FRANCE/FEBRERO/ANATOLE-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\FEBRERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ANATOLE FRANCE\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F123E-16CE-4313-B573-542879B0CE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7574758A-63D3-4F66-A59E-C21848914E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="167">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -524,6 +529,9 @@
   </si>
   <si>
     <t>El mes pasado le pusimos pago al 7C lo que era para el 1B</t>
+  </si>
+  <si>
+    <t>El mes pasado el 8B abono $141.650 y no lo pusimos pago - Creo que se lo pusimos al 7B</t>
   </si>
 </sst>
 </file>
@@ -733,7 +741,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -806,6 +814,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1218,7 +1232,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1473,87 +1487,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1563,6 +1496,98 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="17" fillId="12" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1641,9 +1666,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1681,9 +1706,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1716,9 +1741,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1751,9 +1793,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1928,30 +1987,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="181" t="s">
+      <c r="B1" s="193" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
       <c r="E1" s="63"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="64" t="s">
         <v>26</v>
@@ -1960,16 +2019,16 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="194" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="185"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="195"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -1980,7 +2039,7 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>58</v>
       </c>
@@ -1993,7 +2052,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>59</v>
       </c>
@@ -2004,57 +2063,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="176" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="176"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="186" t="s">
+      <c r="C8" s="188"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="188"/>
+      <c r="C9" s="188"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="196" t="s">
         <v>164</v>
       </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="186"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="186"/>
-      <c r="B14" s="186"/>
-      <c r="C14" s="186"/>
-      <c r="D14" s="186"/>
-      <c r="E14" s="186"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="186"/>
-      <c r="B15" s="186"/>
-      <c r="C15" s="186"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="186"/>
-    </row>
-    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="186"/>
-      <c r="B16" s="186"/>
-      <c r="C16" s="186"/>
-      <c r="D16" s="186"/>
-      <c r="E16" s="186"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="196"/>
+      <c r="C13" s="196"/>
+      <c r="D13" s="196"/>
+      <c r="E13" s="196"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="196"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="196"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+    </row>
+    <row r="16" spans="1:5" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="196"/>
+      <c r="B16" s="196"/>
+      <c r="C16" s="196"/>
+      <c r="D16" s="196"/>
+      <c r="E16" s="196"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2063,7 +2122,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>32</v>
       </c>
@@ -2072,11 +2131,11 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="177" t="s">
+    <row r="22" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="178"/>
+      <c r="B22" s="190"/>
       <c r="C22" s="5"/>
       <c r="D22" s="126">
         <v>803081</v>
@@ -2085,11 +2144,11 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="177" t="s">
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="178"/>
+      <c r="B23" s="190"/>
       <c r="C23" s="5"/>
       <c r="D23" s="126">
         <v>1000830.1</v>
@@ -2098,7 +2157,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="72" t="s">
         <v>133</v>
       </c>
@@ -2109,7 +2168,7 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="72" t="s">
         <v>134</v>
       </c>
@@ -2120,7 +2179,7 @@
       </c>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="55" t="s">
         <v>33</v>
       </c>
@@ -2133,7 +2192,7 @@
       <c r="E26" s="104"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
@@ -2142,28 +2201,28 @@
       <c r="D27" s="126"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="126"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="126"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="128"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
@@ -2172,7 +2231,7 @@
       <c r="D31" s="128"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
         <v>33</v>
       </c>
@@ -2184,7 +2243,7 @@
       </c>
       <c r="E32" s="104"/>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="29" t="s">
         <v>1</v>
       </c>
@@ -2197,7 +2256,7 @@
       </c>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
         <v>18</v>
       </c>
@@ -2206,11 +2265,11 @@
       <c r="D34" s="131"/>
       <c r="E34" s="106"/>
     </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="179" t="s">
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="191" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="180"/>
+      <c r="B35" s="192"/>
       <c r="C35" s="51"/>
       <c r="D35" s="126">
         <v>25000</v>
@@ -2219,11 +2278,11 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="179" t="s">
+    <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="191" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="180"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="51"/>
       <c r="D36" s="126">
         <v>220000</v>
@@ -2232,18 +2291,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="179" t="s">
+    <row r="37" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="191" t="s">
         <v>124</v>
       </c>
-      <c r="B37" s="180"/>
+      <c r="B37" s="192"/>
       <c r="C37" s="51"/>
       <c r="D37" s="132">
         <v>0</v>
       </c>
       <c r="E37" s="107"/>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>15</v>
       </c>
@@ -2255,7 +2314,7 @@
         <v>245000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="34" t="s">
         <v>29</v>
       </c>
@@ -2264,11 +2323,11 @@
       <c r="D39" s="134"/>
       <c r="E39" s="109"/>
     </row>
-    <row r="40" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="177" t="s">
+    <row r="40" spans="1:7" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="189" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="178"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="52"/>
       <c r="D40" s="135">
         <v>176994.85</v>
@@ -2277,11 +2336,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="177" t="s">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="189" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="178"/>
+      <c r="B41" s="190"/>
       <c r="C41" s="52"/>
       <c r="D41" s="136">
         <v>15087.23</v>
@@ -2290,7 +2349,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="29" t="s">
         <v>2</v>
       </c>
@@ -2302,7 +2361,7 @@
         <v>192082.08000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
         <v>16</v>
       </c>
@@ -2311,7 +2370,7 @@
       <c r="D43" s="137"/>
       <c r="E43" s="113"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>44</v>
       </c>
@@ -2325,7 +2384,7 @@
       </c>
       <c r="G44" s="91"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>57</v>
       </c>
@@ -2340,7 +2399,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2357,7 +2416,7 @@
         <v>Transf 12/02</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="str">
         <f>A46</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2374,7 +2433,7 @@
         <v>Transf 12/02</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>3</v>
       </c>
@@ -2386,7 +2445,7 @@
         <v>701934.34</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
         <v>17</v>
       </c>
@@ -2395,7 +2454,7 @@
       <c r="D49" s="137"/>
       <c r="E49" s="113"/>
     </row>
-    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>121</v>
       </c>
@@ -2404,11 +2463,11 @@
       <c r="D50" s="138"/>
       <c r="E50" s="118"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="177" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="189" t="s">
         <v>122</v>
       </c>
-      <c r="B51" s="178"/>
+      <c r="B51" s="190"/>
       <c r="C51" s="5"/>
       <c r="D51" s="138">
         <v>817259.26</v>
@@ -2417,7 +2476,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
         <v>4</v>
       </c>
@@ -2429,14 +2488,14 @@
         <v>817259.26</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="34"/>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
       <c r="D53" s="133"/>
       <c r="E53" s="114"/>
     </row>
-    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="122" t="s">
         <v>61</v>
       </c>
@@ -2449,7 +2508,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="122" t="s">
         <v>131</v>
       </c>
@@ -2462,7 +2521,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
         <v>8</v>
       </c>
@@ -2474,7 +2533,7 @@
         <v>235500</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="34" t="s">
         <v>11</v>
       </c>
@@ -2483,7 +2542,7 @@
       <c r="D57" s="130"/>
       <c r="E57" s="114"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>54</v>
       </c>
@@ -2494,7 +2553,7 @@
       </c>
       <c r="E58" s="116"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
@@ -2506,7 +2565,7 @@
       </c>
       <c r="E59" s="39"/>
     </row>
-    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="50" t="s">
         <v>15</v>
       </c>
@@ -2518,14 +2577,14 @@
         <v>131189.06</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="69"/>
       <c r="E61" s="77"/>
     </row>
-    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="30" t="s">
         <v>47</v>
       </c>
@@ -2534,13 +2593,13 @@
       <c r="D62" s="78"/>
       <c r="E62" s="79"/>
     </row>
-    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="D63" s="80"/>
       <c r="E63" s="81"/>
       <c r="F63" s="42"/>
     </row>
-    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
@@ -2559,7 +2618,7 @@
       <c r="K64" s="91"/>
       <c r="L64" s="91"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D65" s="80"/>
       <c r="E65" s="80"/>
       <c r="H65" s="91"/>
@@ -2568,12 +2627,12 @@
       <c r="K65" s="91"/>
       <c r="L65" s="91"/>
     </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D66" s="80"/>
       <c r="E66" s="80"/>
       <c r="H66" s="124"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>42</v>
       </c>
@@ -2582,35 +2641,35 @@
       <c r="D67" s="84"/>
       <c r="E67" s="85"/>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="177"/>
-      <c r="B68" s="178"/>
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="189"/>
+      <c r="B68" s="190"/>
       <c r="C68" s="5"/>
       <c r="D68" s="95"/>
       <c r="E68" s="71"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="177"/>
-      <c r="B69" s="178"/>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="189"/>
+      <c r="B69" s="190"/>
       <c r="C69" s="5"/>
       <c r="D69" s="73"/>
       <c r="E69" s="71"/>
     </row>
-    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="179"/>
-      <c r="B70" s="180"/>
+    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="191"/>
+      <c r="B70" s="192"/>
       <c r="C70" s="5"/>
       <c r="D70" s="73"/>
       <c r="E70" s="71"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="72"/>
       <c r="B71" s="74"/>
       <c r="C71" s="5"/>
       <c r="D71" s="73"/>
       <c r="E71" s="71"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="48"/>
       <c r="B72" s="47"/>
       <c r="C72" s="47"/>
@@ -2620,9 +2679,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="171" t="s">
         <v>19</v>
       </c>
@@ -2631,8 +2690,8 @@
       <c r="D75" s="173"/>
       <c r="E75" s="174"/>
     </row>
-    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>20</v>
       </c>
@@ -2644,8 +2703,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="67" t="s">
         <v>13</v>
       </c>
@@ -2654,7 +2713,7 @@
         <v>3879170.7400000007</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="67" t="s">
         <v>14</v>
       </c>
@@ -2663,7 +2722,7 @@
         <v>3879170.7400000007</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="67" t="s">
         <v>21</v>
       </c>
@@ -2672,7 +2731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="67" t="s">
         <v>38</v>
       </c>
@@ -2681,61 +2740,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="182"/>
-      <c r="B85" s="182"/>
-      <c r="C85" s="182"/>
-      <c r="D85" s="182"/>
-      <c r="E85" s="182"/>
-    </row>
-    <row r="86" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="182"/>
-      <c r="B86" s="182"/>
-      <c r="C86" s="182"/>
-      <c r="D86" s="182"/>
-      <c r="E86" s="182"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="182"/>
-      <c r="B87" s="182"/>
-      <c r="C87" s="182"/>
-      <c r="D87" s="182"/>
-      <c r="E87" s="182"/>
-    </row>
-    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="197"/>
+      <c r="B85" s="197"/>
+      <c r="C85" s="197"/>
+      <c r="D85" s="197"/>
+      <c r="E85" s="197"/>
+    </row>
+    <row r="86" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="197"/>
+      <c r="B86" s="197"/>
+      <c r="C86" s="197"/>
+      <c r="D86" s="197"/>
+      <c r="E86" s="197"/>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="197"/>
+      <c r="B87" s="197"/>
+      <c r="C87" s="197"/>
+      <c r="D87" s="197"/>
+      <c r="E87" s="197"/>
+    </row>
+    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B89" s="92"/>
       <c r="C89" s="23"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="32"/>
       <c r="B90" s="57">
         <v>0</v>
       </c>
       <c r="C90" s="25"/>
     </row>
-    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B91" s="39">
         <f>PRORRATEO!G31</f>
-        <v>3961860.6800000006</v>
+        <v>4103511.9100000011</v>
       </c>
       <c r="C91" s="23"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="24"/>
       <c r="B92" s="39">
         <v>0</v>
       </c>
       <c r="C92" s="23"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="24" t="s">
         <v>39</v>
       </c>
@@ -2745,19 +2804,19 @@
       </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="27"/>
       <c r="B94" s="46"/>
       <c r="C94" s="23"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="90" t="s">
         <v>43</v>
       </c>
       <c r="B95" s="46"/>
       <c r="C95" s="23"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="38" t="s">
         <v>22</v>
       </c>
@@ -2767,7 +2826,7 @@
       </c>
       <c r="C96" s="23"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
         <v>23</v>
       </c>
@@ -2777,34 +2836,34 @@
       </c>
       <c r="C97" s="23"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B98" s="57">
         <f>SUM(B90:B97)</f>
-        <v>382689.93999999994</v>
+        <v>524341.17000000039</v>
       </c>
       <c r="C98" s="26"/>
       <c r="D98" s="42"/>
     </row>
-    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="40"/>
       <c r="C99" s="26"/>
       <c r="D99" s="42"/>
       <c r="E99" s="93"/>
       <c r="F99" s="94"/>
     </row>
-    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="41"/>
       <c r="C100" s="26"/>
     </row>
-    <row r="101" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="B101" s="40"/>
       <c r="C101" s="36"/>
     </row>
-    <row r="102" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="97" t="s">
         <v>156</v>
       </c>
@@ -2814,7 +2873,7 @@
       <c r="C102" s="36"/>
       <c r="D102" s="45"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="52" t="s">
         <v>48</v>
       </c>
@@ -2823,7 +2882,7 @@
         <v>-3879170.7400000007</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="52" t="s">
         <v>49</v>
       </c>
@@ -2832,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="52" t="s">
         <v>157</v>
       </c>
@@ -2840,7 +2899,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="52" t="s">
         <v>136</v>
       </c>
@@ -2848,7 +2907,7 @@
         <v>320000</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="52" t="s">
         <v>52</v>
       </c>
@@ -2857,43 +2916,43 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="52" t="s">
         <v>50</v>
       </c>
       <c r="B108" s="102">
         <f>PRORRATEO!G31</f>
-        <v>3961860.6800000006</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4103511.9100000011</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B109" s="100">
         <f>SUM(B102:C108)</f>
-        <v>4494194.01</v>
+        <v>4635845.24</v>
       </c>
       <c r="D109" s="42"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="98"/>
       <c r="B110" s="98"/>
     </row>
-    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="183" t="s">
+    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="198" t="s">
         <v>30</v>
       </c>
-      <c r="B112" s="183"/>
-      <c r="C112" s="183"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="183"/>
-      <c r="B113" s="183"/>
-      <c r="C113" s="183"/>
-    </row>
-    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="198"/>
+      <c r="C112" s="198"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="198"/>
+      <c r="B113" s="198"/>
+      <c r="C113" s="198"/>
+    </row>
+    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="87" t="s">
         <v>155</v>
       </c>
@@ -2905,13 +2964,13 @@
       </c>
       <c r="E114" s="103"/>
     </row>
-    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="87"/>
       <c r="B115" s="89"/>
       <c r="C115" s="86"/>
       <c r="D115" s="103"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="43" t="s">
         <v>8</v>
       </c>
@@ -2921,36 +2980,36 @@
       </c>
       <c r="C116" s="44"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M117" s="7"/>
     </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="182"/>
-      <c r="B118" s="182"/>
-      <c r="C118" s="182"/>
-      <c r="D118" s="182"/>
-      <c r="E118" s="182"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="182"/>
-      <c r="B119" s="182"/>
-      <c r="C119" s="182"/>
-      <c r="D119" s="182"/>
-      <c r="E119" s="182"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="182"/>
-      <c r="B120" s="182"/>
-      <c r="C120" s="182"/>
-      <c r="D120" s="182"/>
-      <c r="E120" s="182"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="182"/>
-      <c r="B121" s="182"/>
-      <c r="C121" s="182"/>
-      <c r="D121" s="182"/>
-      <c r="E121" s="182"/>
+    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="197"/>
+      <c r="B118" s="197"/>
+      <c r="C118" s="197"/>
+      <c r="D118" s="197"/>
+      <c r="E118" s="197"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="197"/>
+      <c r="B119" s="197"/>
+      <c r="C119" s="197"/>
+      <c r="D119" s="197"/>
+      <c r="E119" s="197"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="197"/>
+      <c r="B120" s="197"/>
+      <c r="C120" s="197"/>
+      <c r="D120" s="197"/>
+      <c r="E120" s="197"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="197"/>
+      <c r="B121" s="197"/>
+      <c r="C121" s="197"/>
+      <c r="D121" s="197"/>
+      <c r="E121" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -2982,42 +3041,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3041,7 +3100,7 @@
       <c r="M2" s="53"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3056,66 +3115,66 @@
       <c r="L3" s="54"/>
       <c r="M3" s="58"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="187" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="199" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="199" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="187" t="s">
+      <c r="C4" s="199" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="187" t="s">
+      <c r="D4" s="199" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="187" t="s">
+      <c r="E4" s="199" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="197" t="s">
+      <c r="F4" s="209" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="187" t="s">
+      <c r="G4" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="199" t="s">
+      <c r="H4" s="211" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="197" t="s">
+      <c r="I4" s="209" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="197" t="s">
+      <c r="J4" s="209" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="201" t="s">
+      <c r="K4" s="213" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="194" t="s">
+      <c r="M4" s="206" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="189"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="200"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="202"/>
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="201"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="201"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="201"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="210"/>
+      <c r="K5" s="214"/>
       <c r="L5" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/03</v>
       </c>
-      <c r="M5" s="195"/>
-    </row>
-    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="207"/>
+    </row>
+    <row r="6" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="141">
         <v>1</v>
       </c>
@@ -3166,24 +3225,24 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="203">
+    <row r="7" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="176">
         <f>A6+1</f>
         <v>2</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="176" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="203" t="s">
+      <c r="C7" s="176" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="204" t="s">
+      <c r="D7" s="177" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="205">
+      <c r="E7" s="178">
         <v>2.95</v>
       </c>
-      <c r="F7" s="206">
+      <c r="F7" s="179">
         <v>141651.01999999999</v>
       </c>
       <c r="G7" s="152"/>
@@ -3217,7 +3276,7 @@
       </c>
       <c r="O7" s="42"/>
     </row>
-    <row r="8" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="150">
         <f t="shared" ref="A8:A29" si="6">A7+1</f>
         <v>3</v>
@@ -3274,7 +3333,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="141">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3328,7 +3387,7 @@
       </c>
       <c r="P9" s="42"/>
     </row>
-    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="141">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3380,7 +3439,7 @@
       </c>
       <c r="P10" s="42"/>
     </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="141">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3433,7 +3492,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="141">
         <f t="shared" si="6"/>
         <v>7</v>
@@ -3484,7 +3543,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="141">
         <f t="shared" si="6"/>
         <v>8</v>
@@ -3532,7 +3591,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="141">
         <f t="shared" si="6"/>
         <v>9</v>
@@ -3585,7 +3644,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="141">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -3637,7 +3696,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="141">
         <f t="shared" si="6"/>
         <v>11</v>
@@ -3690,7 +3749,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="141">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3744,7 +3803,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="141">
         <f t="shared" si="6"/>
         <v>13</v>
@@ -3797,7 +3856,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="141">
         <f t="shared" si="6"/>
         <v>14</v>
@@ -3848,7 +3907,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="150">
         <f t="shared" si="6"/>
         <v>15</v>
@@ -3899,7 +3958,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="141">
         <f t="shared" si="6"/>
         <v>16</v>
@@ -3950,7 +4009,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="141">
         <f t="shared" si="6"/>
         <v>17</v>
@@ -4000,7 +4059,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="141">
         <f t="shared" si="6"/>
         <v>18</v>
@@ -4052,27 +4111,27 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="203">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="176">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="B24" s="203" t="s">
+      <c r="B24" s="176" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="203" t="s">
+      <c r="C24" s="176" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="204" t="s">
+      <c r="D24" s="177" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="205">
+      <c r="E24" s="178">
         <v>3.43</v>
       </c>
-      <c r="F24" s="206">
+      <c r="F24" s="179">
         <v>154699.19</v>
       </c>
-      <c r="G24" s="207">
+      <c r="G24" s="180">
         <v>141652</v>
       </c>
       <c r="H24" s="144">
@@ -4104,7 +4163,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="141">
         <f t="shared" si="6"/>
         <v>20</v>
@@ -4156,7 +4215,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="141">
         <f t="shared" si="6"/>
         <v>21</v>
@@ -4205,7 +4264,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="141">
         <f t="shared" si="6"/>
         <v>22</v>
@@ -4257,34 +4316,37 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="141">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="181">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="B28" s="158" t="s">
+      <c r="B28" s="182" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="159" t="s">
+      <c r="C28" s="183" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="160" t="s">
+      <c r="D28" s="184" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="166">
+      <c r="E28" s="185">
         <v>2.95</v>
       </c>
-      <c r="F28" s="155">
+      <c r="F28" s="186">
         <v>141651.23000000001</v>
       </c>
-      <c r="G28" s="156"/>
+      <c r="G28" s="186">
+        <f>F28</f>
+        <v>141651.23000000001</v>
+      </c>
       <c r="H28" s="144">
         <f t="shared" si="0"/>
-        <v>141651.23000000001</v>
+        <v>0</v>
       </c>
       <c r="I28" s="144">
         <f t="shared" si="3"/>
-        <v>4249.5369000000001</v>
+        <v>0</v>
       </c>
       <c r="J28" s="145">
         <f t="shared" si="4"/>
@@ -4296,18 +4358,18 @@
       </c>
       <c r="L28" s="147">
         <f t="shared" si="1"/>
-        <v>262618.23</v>
+        <v>116717.23</v>
       </c>
       <c r="M28" s="148">
         <f t="shared" si="2"/>
-        <v>270497.23</v>
+        <v>120219.23</v>
       </c>
       <c r="N28" s="42">
         <f t="shared" si="7"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="141">
         <f t="shared" si="6"/>
         <v>24</v>
@@ -4358,11 +4420,11 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="190" t="s">
+    <row r="30" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="202" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="191"/>
+      <c r="B30" s="203"/>
       <c r="C30" s="159" t="s">
         <v>108</v>
       </c>
@@ -4406,12 +4468,12 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="192" t="s">
+    <row r="31" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="204" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="192"/>
-      <c r="C31" s="193"/>
+      <c r="B31" s="204"/>
+      <c r="C31" s="205"/>
       <c r="D31" s="161"/>
       <c r="E31" s="169">
         <f>SUM(E6:E30)</f>
@@ -4423,15 +4485,15 @@
       </c>
       <c r="G31" s="163">
         <f t="shared" si="8"/>
-        <v>3961860.6800000006</v>
+        <v>4103511.9100000011</v>
       </c>
       <c r="H31" s="163">
         <f t="shared" si="8"/>
-        <v>1174146.5699999998</v>
+        <v>1032495.3399999999</v>
       </c>
       <c r="I31" s="163">
         <f t="shared" si="8"/>
-        <v>35252.017500000002</v>
+        <v>31002.480599999999</v>
       </c>
       <c r="J31" s="164">
         <f t="shared" si="8"/>
@@ -4447,88 +4509,88 @@
       </c>
       <c r="M31" s="165">
         <f>SUM(M6:M30)</f>
-        <v>5428874.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5278596.2500000009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="49"/>
       <c r="D32" s="49"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="182" t="str">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="D34" s="182"/>
-      <c r="E34" s="182"/>
-      <c r="F34" s="182"/>
-      <c r="G34" s="182"/>
-      <c r="H34" s="182"/>
-      <c r="I34" s="182"/>
-      <c r="J34" s="182"/>
-      <c r="K34" s="182"/>
-      <c r="L34" s="182"/>
-    </row>
-    <row r="35" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="182"/>
-      <c r="D35" s="182"/>
-      <c r="E35" s="182"/>
-      <c r="F35" s="182"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="182"/>
-      <c r="I35" s="182"/>
-      <c r="J35" s="182"/>
-      <c r="K35" s="182"/>
-      <c r="L35" s="182"/>
-    </row>
-    <row r="36" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="182"/>
-      <c r="D36" s="182"/>
-      <c r="E36" s="182"/>
-      <c r="F36" s="182"/>
-      <c r="G36" s="182"/>
-      <c r="H36" s="182"/>
-      <c r="I36" s="182"/>
-      <c r="J36" s="182"/>
-      <c r="K36" s="182"/>
-      <c r="L36" s="182"/>
-    </row>
-    <row r="37" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="182"/>
-      <c r="D37" s="182"/>
-      <c r="E37" s="182"/>
-      <c r="F37" s="182"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="182"/>
-      <c r="I37" s="182"/>
-      <c r="J37" s="182"/>
-      <c r="K37" s="182"/>
-      <c r="L37" s="182"/>
-    </row>
-    <row r="38" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="182"/>
-      <c r="D38" s="182"/>
-      <c r="E38" s="182"/>
-      <c r="F38" s="182"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="182"/>
-      <c r="I38" s="182"/>
-      <c r="J38" s="182"/>
-      <c r="K38" s="182"/>
-      <c r="L38" s="182"/>
-    </row>
-    <row r="39" spans="3:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="182"/>
-      <c r="D39" s="182"/>
-      <c r="E39" s="182"/>
-      <c r="F39" s="182"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="182"/>
-      <c r="I39" s="182"/>
-      <c r="J39" s="182"/>
-      <c r="K39" s="182"/>
-      <c r="L39" s="182"/>
+      <c r="D34" s="197"/>
+      <c r="E34" s="197"/>
+      <c r="F34" s="197"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="197"/>
+      <c r="J34" s="197"/>
+      <c r="K34" s="197"/>
+      <c r="L34" s="197"/>
+    </row>
+    <row r="35" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="197"/>
+      <c r="D35" s="197"/>
+      <c r="E35" s="197"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="197"/>
+      <c r="H35" s="197"/>
+      <c r="I35" s="197"/>
+      <c r="J35" s="197"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="197"/>
+    </row>
+    <row r="36" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="197"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="197"/>
+      <c r="G36" s="197"/>
+      <c r="H36" s="197"/>
+      <c r="I36" s="197"/>
+      <c r="J36" s="197"/>
+      <c r="K36" s="197"/>
+      <c r="L36" s="197"/>
+    </row>
+    <row r="37" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="197"/>
+      <c r="D37" s="197"/>
+      <c r="E37" s="197"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="197"/>
+      <c r="L37" s="197"/>
+    </row>
+    <row r="38" spans="3:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="197"/>
+      <c r="D38" s="197"/>
+      <c r="E38" s="197"/>
+      <c r="F38" s="197"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="197"/>
+      <c r="I38" s="197"/>
+      <c r="J38" s="197"/>
+      <c r="K38" s="197"/>
+      <c r="L38" s="197"/>
+    </row>
+    <row r="39" spans="3:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="197"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="197"/>
+      <c r="J39" s="197"/>
+      <c r="K39" s="197"/>
+      <c r="L39" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -4556,12 +4618,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B4:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="187" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
